--- a/DATA/INPUT/phase4_period_assignments.xlsx
+++ b/DATA/INPUT/phase4_period_assignments.xlsx
@@ -449,10 +449,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -497,10 +497,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -513,10 +513,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -529,10 +529,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/INPUT/phase4_period_assignments.xlsx
+++ b/DATA/INPUT/phase4_period_assignments.xlsx
@@ -449,10 +449,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -497,10 +497,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -513,10 +513,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -529,10 +529,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -569,7 +569,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"departments": ["CSE", "DSAI", "ECE"], "section_groups": {"CSE": {"A": 1, "B": 1}, "DSAI": {"A": 2}, "ECE": {"A": 2}}, "sections_by_dept": {"CSE": ["A", "B"], "DSAI": ["A"], "ECE": ["A"]}, "students_per_section": 85}</t>
+          <t>{"departments": ["CSE", "DSAI", "ECE", "AIC"], "section_groups": {"AIC": {"A": 3}, "CSE": {"A": 1, "B": 1}, "DSAI": {"A": 2}, "ECE": {"A": 2}}, "sections_by_dept": {"AIC": ["A"], "CSE": ["A", "B"], "DSAI": ["A"], "ECE": ["A"]}, "students_per_section": 85}</t>
         </is>
       </c>
     </row>
